--- a/기능명세서_학습플래너.xlsx
+++ b/기능명세서_학습플래너.xlsx
@@ -2260,7 +2260,7 @@
     <t xml:space="preserve">이메일, 비밀번호, 닉네임</t>
   </si>
   <si>
-    <t xml:space="preserve">충족하지 못한 조건을 입력 중 실시간으로 표시하고 모두 충족해야 가입 버튼 활성화 / 이메일·닉네임을 포함한 비밀번호와 자주 쓰이는 비밀번호 목록(상위 1만 건)은 거부 / 중복 이메일이면 '이미 가입된 이메일입니다' / bcrypt 해시로 저장</t>
+    <t xml:space="preserve">충족하지 못한 조건을 입력 중 실시간으로 표시하고 모두 충족해야 가입 버튼 활성화 / 이메일·닉네임을 포함한 비밀번호와 자주 쓰이는 비밀번호 목록(상위 1만 건)은 거부 / 중복 이메일이면 '이미 가입된 이메일입니다' / 비밀번호 해싱·저장은 Supabase Auth가 처리</t>
   </si>
   <si>
     <t xml:space="preserve">특수문자 허용 범위를 화면에 명시해야 입력 실패가 줄어듦</t>
@@ -2992,7 +2992,7 @@
     <t xml:space="preserve">카운터 장애 시 이벤트를 큐에 보관하고 복구 후 재집계 / 하루 경계는 사용자 로컬 타임존 기준</t>
   </si>
   <si>
-    <t xml:space="preserve">Redis 카운터</t>
+    <t xml:space="preserve">PostgreSQL 집계 · Redis는 확장 시</t>
   </si>
   <si>
     <t xml:space="preserve">FR-STUDY-04</t>

--- a/기능명세서_학습플래너.xlsx
+++ b/기능명세서_학습플래너.xlsx
@@ -6560,21 +6560,29 @@
       </c>
       <c r="J59" s="56" t="inlineStr">
         <is>
-          <t>Could</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="K59" s="54" t="inlineStr">
         <is>
-          <t>추출 실패 또는 신뢰도 미달이면 미검수 상태로 보관하고 사용자에게 노출하지 않음</t>
-        </is>
-      </c>
-      <c r="L59" s="54" t="n"/>
+          <t>위비티 이용 조건(비영리·원문·포스터 저장 금지, 제목·링크·메타데이터만 사용)과 충돌해 이번 범위에서 제외</t>
+        </is>
+      </c>
+      <c r="L59" s="54" t="inlineStr">
+        <is>
+          <t>포스터 이미지를 받아 저장해야 하는 기능 — 공식 API·제휴로 이미지 사용 허락을 받으면 재검토</t>
+        </is>
+      </c>
       <c r="M59" s="54" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="N59" s="54" t="n"/>
+      <c r="N59" s="54" t="inlineStr">
+        <is>
+          <t>v1.2에서 하향 (Could → Won't, 10-02)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="45.75" customHeight="1" s="44">
       <c r="A60" s="54" t="inlineStr">

--- a/기능명세서_학습플래너.xlsx
+++ b/기능명세서_학습플래너.xlsx
@@ -4873,7 +4873,7 @@
       </c>
       <c r="G32" s="54" t="inlineStr">
         <is>
-          <t>단위당 30~120분 / 선후 관계 표시 / 결과는 고정 JSON 스키마로 반환</t>
+          <t>단위(주제)당 30~600분 — 120분이 넘으면 배치 때 120분 이하 블록 여러 개로 나눔 / 카탈로그 표준 학습시간이 있으면 단위 합을 그에 맞춤 / 선후 관계 표시 / 결과는 고정 JSON 스키마로 반환</t>
         </is>
       </c>
       <c r="H32" s="54" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G33" s="54" t="inlineStr">
         <is>
-          <t>하루 최대 3블록·연속 2시간 초과 금지 / 주 1일 휴식일 확보</t>
+          <t>블록은 최대 120분(긴 단위는 블록 여러 개로 나눠 순서대로) / 하루 최대 3블록·연속 2시간 초과 금지 / 주 1일 휴식일 확보 (일요일을 공부 시간으로 고르면 고르지 않은 요일로)</t>
         </is>
       </c>
       <c r="H33" s="54" t="inlineStr">
@@ -10193,9 +10193,9 @@
   <mergeCells count="10">
     <mergeCell ref="B52:B62"/>
     <mergeCell ref="B18:B30"/>
+    <mergeCell ref="B31:B41"/>
+    <mergeCell ref="B12:B14"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B31:B41"/>
     <mergeCell ref="B70:B71"/>
     <mergeCell ref="B3:B11"/>
     <mergeCell ref="B42:B51"/>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="C44" s="54" t="inlineStr">
         <is>
-          <t>단위는 30~120분 / 선행 관계 명시 / 검색된 커리큘럼 밖의 내용은 추정임을 표시</t>
+          <t>단위(주제)는 30~600분 — 같은 주제 반복은 단위를 쪼개지 않고 시간을 늘림, 배치는 120분 이하 블록으로 / 표준 학습시간이 주어지면 단위 합을 맞춤 / 선행 관계 명시 / 검색된 커리큘럼 밖의 내용은 추정임을 표시</t>
         </is>
       </c>
       <c r="D44" s="79" t="inlineStr">

--- a/기능명세서_학습플래너.xlsx
+++ b/기능명세서_학습플래너.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="작성가이드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="기능명세서" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AI기능명세" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="예시_기능명세서" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="예시_AI기능명세" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성가이드" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능명세서" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비기능명세" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI기능명세" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시_기능명세서" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시_AI기능명세" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기능명세서'!$A$2:$N$200</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'예시_기능명세서'!$A$2:$N$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'비기능명세'!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'예시_기능명세서'!$A$2:$N$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1091,6 +1093,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="21.75" customHeight="1" s="44">
       <c r="A4" s="47" t="inlineStr">
         <is>
@@ -1499,6 +1502,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="21.75" customHeight="1" s="44">
       <c r="A21" s="47" t="inlineStr">
         <is>
@@ -10224,6 +10228,631 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="44" min="1" max="1"/>
+    <col width="10" customWidth="1" style="44" min="2" max="2"/>
+    <col width="14" customWidth="1" style="44" min="3" max="3"/>
+    <col width="58" customWidth="1" style="44" min="4" max="4"/>
+    <col width="40" customWidth="1" style="44" min="5" max="5"/>
+    <col width="46" customWidth="1" style="44" min="6" max="6"/>
+    <col width="10" customWidth="1" style="44" min="7" max="7"/>
+    <col width="22" customWidth="1" style="44" min="8" max="8"/>
+    <col width="36" customWidth="1" style="44" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.5" customHeight="1" s="44">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>ID ★</t>
+        </is>
+      </c>
+      <c r="B1" s="68" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C1" s="68" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D1" s="68" t="inlineStr">
+        <is>
+          <t>요구 내용</t>
+        </is>
+      </c>
+      <c r="E1" s="68" t="inlineStr">
+        <is>
+          <t>측정·검증 기준</t>
+        </is>
+      </c>
+      <c r="F1" s="68" t="inlineStr">
+        <is>
+          <t>구현 위치 (근거)</t>
+        </is>
+      </c>
+      <c r="G1" s="68" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+      <c r="H1" s="68" t="inlineStr">
+        <is>
+          <t>관련 기능</t>
+        </is>
+      </c>
+      <c r="I1" s="68" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="75" customHeight="1" s="44">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t>NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="B2" s="54" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C2" s="54" t="inlineStr">
+        <is>
+          <t>인증 보호</t>
+        </is>
+      </c>
+      <c r="D2" s="54" t="inlineStr">
+        <is>
+          <t>로그인 5회 연속 실패 시 60초 잠금 · 실패 사유 문구 통일로 계정 존재 여부 비노출(로그인·비밀번호 재설정) · 로그인 화면에 비밀번호 조합 규칙 미노출. 단, 회원가입의 중복 이메일은 '이미 가입된 이메일입니다'로 안내 (09-30 팀 결정)</t>
+        </is>
+      </c>
+      <c r="E2" s="54" t="inlineStr">
+        <is>
+          <t>같은 이메일 5회 실패 → 6번째 429 · 없는 이메일/틀린 비밀번호 문구 동일</t>
+        </is>
+      </c>
+      <c r="F2" s="54" t="inlineStr">
+        <is>
+          <t>backend/services/login_guard.py · routers/auth.py · tests/test_login_lock_contest_fix.py</t>
+        </is>
+      </c>
+      <c r="G2" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H2" s="54" t="inlineStr">
+        <is>
+          <t>FR-AUTH-01 · FR-AUTH-03 · FR-JOIN-01</t>
+        </is>
+      </c>
+      <c r="I2" s="54" t="inlineStr">
+        <is>
+          <t>잠금 상태는 서버 메모리 — 서버를 다시 켜면 초기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="75" customHeight="1" s="44">
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>NFR-SEC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="54" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C3" s="54" t="inlineStr">
+        <is>
+          <t>전송·저장 보안</t>
+        </is>
+      </c>
+      <c r="D3" s="54" t="inlineStr">
+        <is>
+          <t>전 구간 HTTPS · OAuth 리프레시 토큰은 애플리케이션 레벨 암호화 저장 · 비밀키는 환경변수로만 주입하고 저장소에 커밋 금지</t>
+        </is>
+      </c>
+      <c r="E3" s="54" t="inlineStr">
+        <is>
+          <t>배포 주소 https · 저장소에 비밀값 0건(커밋 전 검사) · DB 에 OAuth 토큰 컬럼 없음</t>
+        </is>
+      </c>
+      <c r="F3" s="54" t="inlineStr">
+        <is>
+          <t>Vercel·Railway 기본 HTTPS · .gitignore(.env) · routers/google_calendar.py(access_type=online, 읽은 직후 revoke)</t>
+        </is>
+      </c>
+      <c r="G3" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H3" s="54" t="inlineStr">
+        <is>
+          <t>FR-PLAN-01 · FR-AUTH-02</t>
+        </is>
+      </c>
+      <c r="I3" s="54" t="inlineStr">
+        <is>
+          <t>구글 캘린더 토큰을 아예 저장하지 않도록 바꿔 '암호화 저장'보다 강하게 충족 (10-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="75" customHeight="1" s="44">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>NFR-SEC-03</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>비밀번호 정책</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>bcrypt 해시 · 8~64자 영문·숫자·특수문자 각 1자 이상 · 이메일·닉네임 포함 및 상위 1만 건 빈출 비밀번호 거부</t>
+        </is>
+      </c>
+      <c r="E4" s="54" t="inlineStr">
+        <is>
+          <t>규칙 위반 가입·재설정 요청 400 · 입력 중 충족 여부 실시간 표시</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="inlineStr">
+        <is>
+          <t>Supabase Auth(bcrypt) · schemas/user.py · services/password_policy.py · data/common_passwords.txt · frontend/lib/password-feedback.js</t>
+        </is>
+      </c>
+      <c r="G4" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H4" s="54" t="inlineStr">
+        <is>
+          <t>FR-JOIN-01 · FR-AUTH-03</t>
+        </is>
+      </c>
+      <c r="I4" s="54" t="inlineStr">
+        <is>
+          <t>빈출 목록: zxcvbn 4.5.0(MIT) 상위 1만 개</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="75" customHeight="1" s="44">
+      <c r="A5" s="54" t="inlineStr">
+        <is>
+          <t>NFR-SEC-04</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C5" s="54" t="inlineStr">
+        <is>
+          <t>남용 방지</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>비회원 AI 호출 24시간 3회 제한 · IP는 해시로만 보관하고 24시간 후 파기 · 자동화 의심 시 캡차</t>
+        </is>
+      </c>
+      <c r="E5" s="54" t="inlineStr">
+        <is>
+          <t>같은 세션 4번째 추천 429 · 세션을 바꿔도 같은 IP 15회 초과 시 429 · 저장소에 IP 원문 없음</t>
+        </is>
+      </c>
+      <c r="F5" s="54" t="inlineStr">
+        <is>
+          <t>services/goal_limiter.py · routers/goal.py(client_ip) · tests/test_spec_details.py</t>
+        </is>
+      </c>
+      <c r="G5" s="54" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="H5" s="54" t="inlineStr">
+        <is>
+          <t>FR-GOAL-12</t>
+        </is>
+      </c>
+      <c r="I5" s="54" t="inlineStr">
+        <is>
+          <t>캡차는 외부 서비스 가입이 필요해 제외 — 세션+IP 해시 이중 한도와 AI 비용 한도로 대신함</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1" s="44">
+      <c r="A6" s="54" t="inlineStr">
+        <is>
+          <t>NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>개인정보</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>수집 최소화·고지</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>캘린더는 시간대만 사용하고 제목·참석자는 저장·전송하지 않음 · 필수/선택 동의 분리 · 동의 일시 기록 · 최종 로그인 후 12개월 보관</t>
+        </is>
+      </c>
+      <c r="E6" s="54" t="inlineStr">
+        <is>
+          <t>캘린더 권한 범위 calendar.freebusy 1개 · users.agreed_at · 개인정보 처리방침 고지</t>
+        </is>
+      </c>
+      <c r="F6" s="54" t="inlineStr">
+        <is>
+          <t>routers/google_calendar.py · components/SignupConsentFields.js · routers/auth.py · app/privacy/page.js</t>
+        </is>
+      </c>
+      <c r="G6" s="54" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="H6" s="54" t="inlineStr">
+        <is>
+          <t>FR-JOIN-02 · FR-PLAN-01 · FR-MAIN-06</t>
+        </is>
+      </c>
+      <c r="I6" s="54" t="inlineStr">
+        <is>
+          <t>'최종 로그인 후 12개월' 휴면 계정 자동 삭제는 미구현 (탈퇴 프로필 1년 보관 후 삭제는 구현)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1" s="44">
+      <c r="A7" s="54" t="inlineStr">
+        <is>
+          <t>NFR-PRIV-02</t>
+        </is>
+      </c>
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>개인정보</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>삭제권</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>메모리 항목별·전체 즉시 물리 삭제 · 탈퇴 시 일정·학습기록·메모리·캘린더 토큰 전체 삭제(최대 24시간) · 토큰은 즉시 폐기</t>
+        </is>
+      </c>
+      <c r="E7" s="54" t="inlineStr">
+        <is>
+          <t>삭제 API 후 행 0건 · 탈퇴 시 auth.users 삭제 → 외래키 cascade</t>
+        </is>
+      </c>
+      <c r="F7" s="54" t="inlineStr">
+        <is>
+          <t>routers/memories.py · routers/settings.py(withdraw) · migrations/010_withdrawal_retention.sql</t>
+        </is>
+      </c>
+      <c r="G7" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H7" s="54" t="inlineStr">
+        <is>
+          <t>FR-MEM-02 · FR-MY-04</t>
+        </is>
+      </c>
+      <c r="I7" s="54" t="inlineStr">
+        <is>
+          <t>캘린더 토큰은 저장하지 않으므로 지울 것이 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1" s="44">
+      <c r="A8" s="54" t="inlineStr">
+        <is>
+          <t>NFR-ETHIC-01</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>AI 윤리</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>AI 생성 고지</t>
+        </is>
+      </c>
+      <c r="D8" s="54" t="inlineStr">
+        <is>
+          <t>AI가 생성한 목표·일정·추천 이유에 'AI 추천' 배지와 부정확 가능성 문구 상시 노출 · 접거나 숨길 수 없음 · 비회원 화면에도 동일 적용</t>
+        </is>
+      </c>
+      <c r="E8" s="54" t="inlineStr">
+        <is>
+          <t>온보딩·계획·공모전 추천 화면에 배지와 문구 노출 · 가입 시 AI 고지 동의, 문구가 바뀌면 재동의</t>
+        </is>
+      </c>
+      <c r="F8" s="54" t="inlineStr">
+        <is>
+          <t>components/AiNotice.js · app/onboarding · components/PlanBuilder.js · components/ContestCard.js · components/ReconsentGate.js</t>
+        </is>
+      </c>
+      <c r="G8" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H8" s="54" t="inlineStr">
+        <is>
+          <t>FR-JOIN-03 · FR-GOAL-05 · FR-CONT-05</t>
+        </is>
+      </c>
+      <c r="I8" s="54" t="inlineStr"/>
+    </row>
+    <row r="9" ht="75" customHeight="1" s="44">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>NFR-ETHIC-02</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>AI 윤리</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>사실성</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>검색된 공고 원문에 없는 내용 생성 금지 · 지원 자격 충족을 단정하지 않고 원문 확인 안내 병기</t>
+        </is>
+      </c>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>추천 이유 사실성 100% (AI 품질 평가 3차) · 기간 계산과 반대인 AI 이유는 템플릿으로 교체</t>
+        </is>
+      </c>
+      <c r="F9" s="54" t="inlineStr">
+        <is>
+          <t>services/contest_recommender.py · services/goal_recommender.py(reason_consistent) · backend/evals/RESULTS.md</t>
+        </is>
+      </c>
+      <c r="G9" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H9" s="54" t="inlineStr">
+        <is>
+          <t>FR-CONT-05 · FR-GOAL-05</t>
+        </is>
+      </c>
+      <c r="I9" s="54" t="inlineStr"/>
+    </row>
+    <row r="10" ht="75" customHeight="1" s="44">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t>NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>성능</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>응답 성능</t>
+        </is>
+      </c>
+      <c r="D10" s="54" t="inlineStr">
+        <is>
+          <t>일반 조회 p95 1초 이내 · AI 생성 20초 타임아웃 · 학습 분해 에이전트는 전체 60초 + 실제 진행 단계 표시 · RAG 검색 5초 타임아웃 후 태그 겹침 검색으로 대체</t>
+        </is>
+      </c>
+      <c r="E10" s="54" t="inlineStr">
+        <is>
+          <t>에이전트 실측 41~46초 · RAG 관련성 실측 0.9~2.3초 · 시간 초과 시 대체 경로로 응답</t>
+        </is>
+      </c>
+      <c r="F10" s="54" t="inlineStr">
+        <is>
+          <t>services/decomposer.py(LLM_BUDGET_SECONDS=60) · services/goal_claude.py(5초) · goal_recommender(20초) · POST /plan/decompose/stream</t>
+        </is>
+      </c>
+      <c r="G10" s="54" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="H10" s="54" t="inlineStr">
+        <is>
+          <t>FR-PLAN-02 · FR-GOAL-03 · FR-GOAL-05</t>
+        </is>
+      </c>
+      <c r="I10" s="54" t="inlineStr">
+        <is>
+          <t>일반 조회 p95 는 배포 후 측정 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1" s="44">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>가용성</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>부분 장애 허용</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr">
+        <is>
+          <t>AI·캘린더·알림 중 하나가 실패해도 나머지 기능은 정상 동작 · 집계 실패 시 직전 값 유지</t>
+        </is>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>AI 키 없음·시간 초과·비용 한도에서도 계획 생성 · 알림 작업 하나 실패해도 워커 계속</t>
+        </is>
+      </c>
+      <c r="F11" s="54" t="inlineStr">
+        <is>
+          <t>services/llm.py(None → 대체) · services/template.py · workers/notification_worker.py(_safe) · 야간 재조정 실패 시 기존 일정 유지</t>
+        </is>
+      </c>
+      <c r="G11" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H11" s="54" t="inlineStr">
+        <is>
+          <t>FR-PLAN-02 · FR-PLAN-06 · FR-ALARM-01~04</t>
+        </is>
+      </c>
+      <c r="I11" s="54" t="inlineStr"/>
+    </row>
+    <row r="12" ht="75" customHeight="1" s="44">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>NFR-COST-01</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>비용 상한</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>일일 API 비용 임계치 도달 시 신규 AI 호출 차단(비AI 기능 유지) · 비회원 추천을 먼저 차단 · 기능별 비용 분리 집계</t>
+        </is>
+      </c>
+      <c r="E12" s="54" t="inlineStr">
+        <is>
+          <t>한도 80% 비회원 AI 차단 · 100% 전체 AI 차단 후 규칙으로 대체 · 관리자 화면에 기능별 호출 수</t>
+        </is>
+      </c>
+      <c r="F12" s="54" t="inlineStr">
+        <is>
+          <t>services/ai_budget.py · GET /admin/ai-budget · components/AdminAiBudget.js</t>
+        </is>
+      </c>
+      <c r="G12" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H12" s="54" t="inlineStr">
+        <is>
+          <t>FR-ADMIN-02 · FR-GOAL-12</t>
+        </is>
+      </c>
+      <c r="I12" s="54" t="inlineStr">
+        <is>
+          <t>게이트웨이가 청구액을 주지 않아 호출 수 × 모델별 예상 단가로 어림 (AI_DAILY_BUDGET_USD, 기본 5달러)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1" s="44">
+      <c r="A13" s="54" t="inlineStr">
+        <is>
+          <t>NFR-A11Y-01</t>
+        </is>
+      </c>
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>접근성</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>접근성</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>적응형 테마가 바뀌어도 명도 대비는 레벨과 무관하게 WCAG AA 유지 · 색만으로 상태를 구분하지 않음(진도 신호등에 문구 병기)</t>
+        </is>
+      </c>
+      <c r="E13" s="54" t="inlineStr">
+        <is>
+          <t>진도·알림·공고 상태에 항상 문구 병기 · 레벨별 테마 색은 대비 4.5:1 이상 토큰만 사용</t>
+        </is>
+      </c>
+      <c r="F13" s="54" t="inlineStr">
+        <is>
+          <t>frontend/lib/ui.js(paceView 문구) · app/globals.css(색 토큰) · components/AdaptiveTheme.js</t>
+        </is>
+      </c>
+      <c r="G13" s="54" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H13" s="54" t="inlineStr">
+        <is>
+          <t>FR-UI-01 · FR-PACE-04</t>
+        </is>
+      </c>
+      <c r="I13" s="54" t="inlineStr">
+        <is>
+          <t>자동 대비 측정 도구 결과는 발표 전 첨부 예정</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -10254,6 +10883,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="44">
       <c r="A4" s="77" t="inlineStr">
         <is>
@@ -10492,6 +11122,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="44">
       <c r="A15" s="77" t="inlineStr">
         <is>
@@ -12738,7 +13370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15945,7 +16577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15977,6 +16609,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="44">
       <c r="A4" s="77" t="inlineStr">
         <is>
@@ -16151,6 +16784,8 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="44">
       <c r="A13" s="77" t="inlineStr">
         <is>
